--- a/MAL_slangebeskrivelse_flere_rader.xlsx
+++ b/MAL_slangebeskrivelse_flere_rader.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\script_2\nuitka\my_slangeprogram\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\script_2\nuitka\my_slangeprogram\slangeprogram ny\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{B2E555B7-2C59-490F-9444-A27964EF1758}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{500AB234-8143-46A1-97CD-6137ECF7ADC4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{4B9EA1DB-C32F-4780-89D6-3C7CFAC12FB3}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{4B9EA1DB-C32F-4780-89D6-3C7CFAC12FB3}"/>
   </bookViews>
   <sheets>
     <sheet name="Ark1" sheetId="1" r:id="rId1"/>
@@ -36,12 +36,9 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6" uniqueCount="6">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5" uniqueCount="5">
   <si>
     <t>Slangebeskrivelse</t>
-  </si>
-  <si>
-    <t>Materiale</t>
   </si>
   <si>
     <t>Lager</t>
@@ -434,13 +431,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A0C4847B-D7D8-4FEC-8C14-64F2E530DCB2}">
-  <dimension ref="A1:F1"/>
+  <dimension ref="A1:E1"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="18.5703125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="45" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -456,9 +453,6 @@
       <c r="E1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" t="s">
-        <v>5</v>
-      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
